--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.beta.carotene/RANDOMSEARCH_DETAILS_total.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.beta.carotene/RANDOMSEARCH_DETAILS_total.beta.carotene.xlsx
@@ -413,9 +413,4084 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Pretraitement</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code_R_Pretraitement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meilleurs_Hyperparam_RF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RMSEC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RMSECV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(1,3,5))</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.3031</v>
+      </c>
+      <c r="G2" t="n">
+        <v>84.99939999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>242.7828</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.3149</v>
+      </c>
+      <c r="G3" t="n">
+        <v>90.5548</v>
+      </c>
+      <c r="H3" t="n">
+        <v>247.4849</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9802</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.4176</v>
+      </c>
+      <c r="G4" t="n">
+        <v>101.6348</v>
+      </c>
+      <c r="H4" t="n">
+        <v>284.9638</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,700,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.9272</v>
+      </c>
+      <c r="G5" t="n">
+        <v>267.8481</v>
+      </c>
+      <c r="H5" t="n">
+        <v>424.6444</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,750,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8292</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.8776</v>
+      </c>
+      <c r="G6" t="n">
+        <v>265.2125</v>
+      </c>
+      <c r="H6" t="n">
+        <v>413.1256</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1000,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.3568</v>
+      </c>
+      <c r="G7" t="n">
+        <v>98.1326</v>
+      </c>
+      <c r="H7" t="n">
+        <v>263.4095</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9563</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.3957</v>
+      </c>
+      <c r="G8" t="n">
+        <v>138.629</v>
+      </c>
+      <c r="H8" t="n">
+        <v>277.4093</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1200,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9877</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.3004</v>
+      </c>
+      <c r="G9" t="n">
+        <v>84.3352</v>
+      </c>
+      <c r="H9" t="n">
+        <v>241.6851</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9542</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.4002</v>
+      </c>
+      <c r="G10" t="n">
+        <v>140.8903</v>
+      </c>
+      <c r="H10" t="n">
+        <v>278.971</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9581</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.3943</v>
+      </c>
+      <c r="G11" t="n">
+        <v>136.3509</v>
+      </c>
+      <c r="H11" t="n">
+        <v>276.924</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9707</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.3923</v>
+      </c>
+      <c r="G12" t="n">
+        <v>117.9594</v>
+      </c>
+      <c r="H12" t="n">
+        <v>276.213</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9574</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.3977</v>
+      </c>
+      <c r="G13" t="n">
+        <v>137.3413</v>
+      </c>
+      <c r="H13" t="n">
+        <v>278.0967</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="G14" t="n">
+        <v>136.5079</v>
+      </c>
+      <c r="H14" t="n">
+        <v>277.1586</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9708</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.3904</v>
+      </c>
+      <c r="G15" t="n">
+        <v>117.9355</v>
+      </c>
+      <c r="H15" t="n">
+        <v>275.5403</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9575</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.3927</v>
+      </c>
+      <c r="G16" t="n">
+        <v>136.8027</v>
+      </c>
+      <c r="H16" t="n">
+        <v>276.3548</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9572000000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="G17" t="n">
+        <v>137.3898</v>
+      </c>
+      <c r="H17" t="n">
+        <v>276.8189</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="G18" t="n">
+        <v>87.6422</v>
+      </c>
+      <c r="H18" t="n">
+        <v>244.7522</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9841</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.3053</v>
+      </c>
+      <c r="G19" t="n">
+        <v>90.82470000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>243.6615</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9839</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.3136</v>
+      </c>
+      <c r="G20" t="n">
+        <v>90.0939</v>
+      </c>
+      <c r="H20" t="n">
+        <v>246.9445</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="G21" t="n">
+        <v>90.28919999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>251.0179</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.3253</v>
+      </c>
+      <c r="G22" t="n">
+        <v>92.0608</v>
+      </c>
+      <c r="H22" t="n">
+        <v>251.5207</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="G23" t="n">
+        <v>95.0802</v>
+      </c>
+      <c r="H23" t="n">
+        <v>250.6197</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9821</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.3299</v>
+      </c>
+      <c r="G24" t="n">
+        <v>92.8065</v>
+      </c>
+      <c r="H24" t="n">
+        <v>253.2946</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9805</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.3302</v>
+      </c>
+      <c r="G25" t="n">
+        <v>96.82729999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>253.4179</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.2929</v>
+      </c>
+      <c r="G26" t="n">
+        <v>85.0137</v>
+      </c>
+      <c r="H26" t="n">
+        <v>238.6477</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.3066</v>
+      </c>
+      <c r="G27" t="n">
+        <v>88.79859999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>244.2007</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.3047</v>
+      </c>
+      <c r="G28" t="n">
+        <v>87.96420000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>243.4164</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9842</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.3093</v>
+      </c>
+      <c r="G29" t="n">
+        <v>91.289</v>
+      </c>
+      <c r="H29" t="n">
+        <v>245.276</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.3055</v>
+      </c>
+      <c r="G30" t="n">
+        <v>88.2581</v>
+      </c>
+      <c r="H30" t="n">
+        <v>243.7664</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="G31" t="n">
+        <v>91.1857</v>
+      </c>
+      <c r="H31" t="n">
+        <v>247.697</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9819</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.3158</v>
+      </c>
+      <c r="G32" t="n">
+        <v>95.2513</v>
+      </c>
+      <c r="H32" t="n">
+        <v>247.8144</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9824000000000001</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.3172</v>
+      </c>
+      <c r="G33" t="n">
+        <v>93.6559</v>
+      </c>
+      <c r="H33" t="n">
+        <v>248.3654</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.3544</v>
+      </c>
+      <c r="G34" t="n">
+        <v>108.8336</v>
+      </c>
+      <c r="H34" t="n">
+        <v>262.5231</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.3343</v>
+      </c>
+      <c r="G35" t="n">
+        <v>92.81229999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>254.9906</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.3088</v>
+      </c>
+      <c r="G36" t="n">
+        <v>94.2372</v>
+      </c>
+      <c r="H36" t="n">
+        <v>245.0416</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.2967</v>
+      </c>
+      <c r="G37" t="n">
+        <v>86.1853</v>
+      </c>
+      <c r="H37" t="n">
+        <v>240.2254</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9868</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.2936</v>
+      </c>
+      <c r="G38" t="n">
+        <v>84.74339999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>238.9685</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9853</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.3003</v>
+      </c>
+      <c r="G39" t="n">
+        <v>88.0639</v>
+      </c>
+      <c r="H39" t="n">
+        <v>241.6437</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.3205</v>
+      </c>
+      <c r="G40" t="n">
+        <v>89.1498</v>
+      </c>
+      <c r="H40" t="n">
+        <v>249.671</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.3553</v>
+      </c>
+      <c r="G41" t="n">
+        <v>108.7932</v>
+      </c>
+      <c r="H41" t="n">
+        <v>262.8632</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.3348</v>
+      </c>
+      <c r="G42" t="n">
+        <v>92.9547</v>
+      </c>
+      <c r="H42" t="n">
+        <v>255.1618</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9868</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.3084</v>
+      </c>
+      <c r="G43" t="n">
+        <v>93.1755</v>
+      </c>
+      <c r="H43" t="n">
+        <v>244.8992</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9868</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="G44" t="n">
+        <v>85.69580000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>240.3427</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.2928</v>
+      </c>
+      <c r="G45" t="n">
+        <v>83.88849999999999</v>
+      </c>
+      <c r="H45" t="n">
+        <v>238.6262</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.3067</v>
+      </c>
+      <c r="G46" t="n">
+        <v>89.22750000000001</v>
+      </c>
+      <c r="H46" t="n">
+        <v>244.2271</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.3228</v>
+      </c>
+      <c r="G47" t="n">
+        <v>89.7504</v>
+      </c>
+      <c r="H47" t="n">
+        <v>250.5579</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1400,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9855</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="G48" t="n">
+        <v>91.2944</v>
+      </c>
+      <c r="H48" t="n">
+        <v>247.889</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(40,1300,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9874000000000001</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.3083</v>
+      </c>
+      <c r="G49" t="n">
+        <v>87.354</v>
+      </c>
+      <c r="H49" t="n">
+        <v>244.8483</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9278999999999999</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.7551</v>
+      </c>
+      <c r="G50" t="n">
+        <v>201.5565</v>
+      </c>
+      <c r="H50" t="n">
+        <v>383.2076</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9684</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.8188</v>
+      </c>
+      <c r="G51" t="n">
+        <v>147.8475</v>
+      </c>
+      <c r="H51" t="n">
+        <v>399.0554</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9669</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.8127</v>
+      </c>
+      <c r="G52" t="n">
+        <v>150.2996</v>
+      </c>
+      <c r="H52" t="n">
+        <v>397.5567</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.7933</v>
+      </c>
+      <c r="G53" t="n">
+        <v>185.1054</v>
+      </c>
+      <c r="H53" t="n">
+        <v>392.7782</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8994</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.7714</v>
+      </c>
+      <c r="G54" t="n">
+        <v>232.1317</v>
+      </c>
+      <c r="H54" t="n">
+        <v>387.3201</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9717</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.8518</v>
+      </c>
+      <c r="G55" t="n">
+        <v>154.2184</v>
+      </c>
+      <c r="H55" t="n">
+        <v>407.0072</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9612000000000001</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.8621</v>
+      </c>
+      <c r="G56" t="n">
+        <v>185.5029</v>
+      </c>
+      <c r="H56" t="n">
+        <v>409.4665</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,650,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8939</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.8454</v>
+      </c>
+      <c r="G57" t="n">
+        <v>239.302</v>
+      </c>
+      <c r="H57" t="n">
+        <v>405.465</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,15))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.8786</v>
+      </c>
+      <c r="G58" t="n">
+        <v>266.5484</v>
+      </c>
+      <c r="H58" t="n">
+        <v>413.3565</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,21))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.881</v>
+      </c>
+      <c r="G59" t="n">
+        <v>285.9397</v>
+      </c>
+      <c r="H59" t="n">
+        <v>413.9315</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,25))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.8811</v>
+      </c>
+      <c r="G60" t="n">
+        <v>285.8089</v>
+      </c>
+      <c r="H60" t="n">
+        <v>413.9584</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7901</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.8855</v>
+      </c>
+      <c r="G61" t="n">
+        <v>286.4174</v>
+      </c>
+      <c r="H61" t="n">
+        <v>414.9748</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.8218</v>
+      </c>
+      <c r="G62" t="n">
+        <v>246.317</v>
+      </c>
+      <c r="H62" t="n">
+        <v>399.7841</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8695000000000001</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.8179</v>
+      </c>
+      <c r="G63" t="n">
+        <v>247.2063</v>
+      </c>
+      <c r="H63" t="n">
+        <v>398.8272</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8321</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.822</v>
+      </c>
+      <c r="G64" t="n">
+        <v>270.9963</v>
+      </c>
+      <c r="H64" t="n">
+        <v>399.8288</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8254</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.8224</v>
+      </c>
+      <c r="G65" t="n">
+        <v>272.3274</v>
+      </c>
+      <c r="H65" t="n">
+        <v>399.9104</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9157</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.8232</v>
+      </c>
+      <c r="G66" t="n">
+        <v>217.0733</v>
+      </c>
+      <c r="H66" t="n">
+        <v>400.1251</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,700,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.8924</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.8422</v>
+      </c>
+      <c r="G67" t="n">
+        <v>253.4685</v>
+      </c>
+      <c r="H67" t="n">
+        <v>404.7145</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.8855</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.8415</v>
+      </c>
+      <c r="G68" t="n">
+        <v>250.0693</v>
+      </c>
+      <c r="H68" t="n">
+        <v>404.5423</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.3521</v>
+      </c>
+      <c r="G69" t="n">
+        <v>90.55840000000001</v>
+      </c>
+      <c r="H69" t="n">
+        <v>261.6721</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>73</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.3424</v>
+      </c>
+      <c r="G70" t="n">
+        <v>90.31359999999999</v>
+      </c>
+      <c r="H70" t="n">
+        <v>258.0411</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>74</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="G71" t="n">
+        <v>90.5667</v>
+      </c>
+      <c r="H71" t="n">
+        <v>260.1325</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>75</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.3342</v>
+      </c>
+      <c r="G72" t="n">
+        <v>96.1378</v>
+      </c>
+      <c r="H72" t="n">
+        <v>254.9372</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>76</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.3629</v>
+      </c>
+      <c r="G73" t="n">
+        <v>96.4875</v>
+      </c>
+      <c r="H73" t="n">
+        <v>265.6672</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.3479</v>
+      </c>
+      <c r="G74" t="n">
+        <v>91.5039</v>
+      </c>
+      <c r="H74" t="n">
+        <v>260.1136</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.3716</v>
+      </c>
+      <c r="G75" t="n">
+        <v>113.2153</v>
+      </c>
+      <c r="H75" t="n">
+        <v>268.8362</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.3716</v>
+      </c>
+      <c r="G76" t="n">
+        <v>113.2153</v>
+      </c>
+      <c r="H76" t="n">
+        <v>268.8362</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>80</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8756</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.8164</v>
+      </c>
+      <c r="G77" t="n">
+        <v>238.2525</v>
+      </c>
+      <c r="H77" t="n">
+        <v>398.4714</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>81</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.8645</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.8153</v>
+      </c>
+      <c r="G78" t="n">
+        <v>246.0755</v>
+      </c>
+      <c r="H78" t="n">
+        <v>398.1966</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.8435</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.8134</v>
+      </c>
+      <c r="G79" t="n">
+        <v>258.1432</v>
+      </c>
+      <c r="H79" t="n">
+        <v>397.7348</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.8646</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.8146</v>
+      </c>
+      <c r="G80" t="n">
+        <v>245.9642</v>
+      </c>
+      <c r="H80" t="n">
+        <v>398.0147</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.8804999999999999</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.828</v>
+      </c>
+      <c r="G81" t="n">
+        <v>245.7316</v>
+      </c>
+      <c r="H81" t="n">
+        <v>401.2864</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>85</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.9187</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.8059</v>
+      </c>
+      <c r="G82" t="n">
+        <v>213.6923</v>
+      </c>
+      <c r="H82" t="n">
+        <v>395.9014</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>86</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9718</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.3712</v>
+      </c>
+      <c r="G83" t="n">
+        <v>115.321</v>
+      </c>
+      <c r="H83" t="n">
+        <v>268.6656</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>87</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9716</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.3753</v>
+      </c>
+      <c r="G84" t="n">
+        <v>115.658</v>
+      </c>
+      <c r="H84" t="n">
+        <v>270.1676</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.3704</v>
+      </c>
+      <c r="G85" t="n">
+        <v>115.0063</v>
+      </c>
+      <c r="H85" t="n">
+        <v>268.3743</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9752999999999999</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.3242</v>
+      </c>
+      <c r="G86" t="n">
+        <v>109.343</v>
+      </c>
+      <c r="H86" t="n">
+        <v>251.1031</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="G87" t="n">
+        <v>88.0476</v>
+      </c>
+      <c r="H87" t="n">
+        <v>251.0207</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.3118</v>
+      </c>
+      <c r="G88" t="n">
+        <v>89.09399999999999</v>
+      </c>
+      <c r="H88" t="n">
+        <v>246.26</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>92</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.3215</v>
+      </c>
+      <c r="G89" t="n">
+        <v>87.98609999999999</v>
+      </c>
+      <c r="H89" t="n">
+        <v>250.062</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>93</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9868</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.3082</v>
+      </c>
+      <c r="G90" t="n">
+        <v>93.1755</v>
+      </c>
+      <c r="H90" t="n">
+        <v>244.8195</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>94</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9868</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.2969</v>
+      </c>
+      <c r="G91" t="n">
+        <v>85.7488</v>
+      </c>
+      <c r="H91" t="n">
+        <v>240.2948</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.3118</v>
+      </c>
+      <c r="G92" t="n">
+        <v>89.09399999999999</v>
+      </c>
+      <c r="H92" t="n">
+        <v>246.26</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>96</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9868</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.2969</v>
+      </c>
+      <c r="G93" t="n">
+        <v>85.7488</v>
+      </c>
+      <c r="H93" t="n">
+        <v>240.2948</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>97</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.9802</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.4176</v>
+      </c>
+      <c r="G94" t="n">
+        <v>101.6348</v>
+      </c>
+      <c r="H94" t="n">
+        <v>284.9638</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>98</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.9287</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.0817</v>
+      </c>
+      <c r="G95" t="n">
+        <v>227.5826</v>
+      </c>
+      <c r="H95" t="n">
+        <v>458.6506</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>99</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9772999999999999</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.4196</v>
+      </c>
+      <c r="G96" t="n">
+        <v>104.3345</v>
+      </c>
+      <c r="H96" t="n">
+        <v>285.6727</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9776</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.4181</v>
+      </c>
+      <c r="G97" t="n">
+        <v>103.6314</v>
+      </c>
+      <c r="H97" t="n">
+        <v>285.1525</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9748</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.3067</v>
+      </c>
+      <c r="G98" t="n">
+        <v>109.6479</v>
+      </c>
+      <c r="H98" t="n">
+        <v>244.2208</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>102</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.2915</v>
+      </c>
+      <c r="G99" t="n">
+        <v>106.4958</v>
+      </c>
+      <c r="H99" t="n">
+        <v>238.077</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>103</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9784</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.3105</v>
+      </c>
+      <c r="G100" t="n">
+        <v>103.2454</v>
+      </c>
+      <c r="H100" t="n">
+        <v>245.738</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9756</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.3139</v>
+      </c>
+      <c r="G101" t="n">
+        <v>109.0375</v>
+      </c>
+      <c r="H101" t="n">
+        <v>247.0704</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.9819</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.3276</v>
+      </c>
+      <c r="G102" t="n">
+        <v>97.9212</v>
+      </c>
+      <c r="H102" t="n">
+        <v>252.3907</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9795</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.3055</v>
+      </c>
+      <c r="G103" t="n">
+        <v>104.1047</v>
+      </c>
+      <c r="H103" t="n">
+        <v>243.754</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.9847</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.2986</v>
+      </c>
+      <c r="G104" t="n">
+        <v>91.8711</v>
+      </c>
+      <c r="H104" t="n">
+        <v>240.9913</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9796</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.2948</v>
+      </c>
+      <c r="G105" t="n">
+        <v>101.2133</v>
+      </c>
+      <c r="H105" t="n">
+        <v>239.4496</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>109</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9819</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.2898</v>
+      </c>
+      <c r="G106" t="n">
+        <v>93.8601</v>
+      </c>
+      <c r="H106" t="n">
+        <v>237.3817</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>110</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9762999999999999</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.3067</v>
+      </c>
+      <c r="G107" t="n">
+        <v>106.9456</v>
+      </c>
+      <c r="H107" t="n">
+        <v>244.2215</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>111</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.3623</v>
+      </c>
+      <c r="G108" t="n">
+        <v>96.0966</v>
+      </c>
+      <c r="H108" t="n">
+        <v>265.4489</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>112</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.3378</v>
+      </c>
+      <c r="G109" t="n">
+        <v>93.877</v>
+      </c>
+      <c r="H109" t="n">
+        <v>256.3082</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>113</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9855</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.3141</v>
+      </c>
+      <c r="G110" t="n">
+        <v>90.9375</v>
+      </c>
+      <c r="H110" t="n">
+        <v>247.1612</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>114</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9856</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.3205</v>
+      </c>
+      <c r="G111" t="n">
+        <v>90.53879999999999</v>
+      </c>
+      <c r="H111" t="n">
+        <v>249.6726</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>115</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.362</v>
+      </c>
+      <c r="G112" t="n">
+        <v>96.0967</v>
+      </c>
+      <c r="H112" t="n">
+        <v>265.3187</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>116</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.3378</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.7349</v>
+      </c>
+      <c r="H113" t="n">
+        <v>256.3257</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>117</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.3196</v>
+      </c>
+      <c r="G114" t="n">
+        <v>90.8571</v>
+      </c>
+      <c r="H114" t="n">
+        <v>249.3044</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>118</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.3215</v>
+      </c>
+      <c r="G115" t="n">
+        <v>90.7064</v>
+      </c>
+      <c r="H115" t="n">
+        <v>250.0428</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>119</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.9733000000000001</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.8713</v>
+      </c>
+      <c r="G116" t="n">
+        <v>151.8694</v>
+      </c>
+      <c r="H116" t="n">
+        <v>411.6475</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>120</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.8654</v>
+      </c>
+      <c r="G117" t="n">
+        <v>157.9737</v>
+      </c>
+      <c r="H117" t="n">
+        <v>410.2496</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>121</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9796</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.2948</v>
+      </c>
+      <c r="G118" t="n">
+        <v>101.2133</v>
+      </c>
+      <c r="H118" t="n">
+        <v>239.4496</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>122</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.3378</v>
+      </c>
+      <c r="G119" t="n">
+        <v>93.7349</v>
+      </c>
+      <c r="H119" t="n">
+        <v>256.3257</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>123</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.9603</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.3844</v>
+      </c>
+      <c r="G120" t="n">
+        <v>133.5987</v>
+      </c>
+      <c r="H120" t="n">
+        <v>273.4298</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>124</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.9603</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.3844</v>
+      </c>
+      <c r="G121" t="n">
+        <v>133.5987</v>
+      </c>
+      <c r="H121" t="n">
+        <v>273.4298</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>125</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9816</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.3181</v>
+      </c>
+      <c r="G122" t="n">
+        <v>95.33329999999999</v>
+      </c>
+      <c r="H122" t="n">
+        <v>248.741</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>126</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.3379</v>
+      </c>
+      <c r="G123" t="n">
+        <v>93.7483</v>
+      </c>
+      <c r="H123" t="n">
+        <v>256.339</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9857</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.3226</v>
+      </c>
+      <c r="G124" t="n">
+        <v>91.43129999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>250.4622</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>172</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.3185</v>
+      </c>
+      <c r="G125" t="n">
+        <v>89.59480000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>248.8902</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>173</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.3758</v>
+      </c>
+      <c r="G126" t="n">
+        <v>97.7538</v>
+      </c>
+      <c r="H126" t="n">
+        <v>270.3472</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>174</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.3006</v>
+      </c>
+      <c r="G127" t="n">
+        <v>92.2045</v>
+      </c>
+      <c r="H127" t="n">
+        <v>241.7878</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.beta.carotene/RANDOMSEARCH_DETAILS_total.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.beta.carotene/RANDOMSEARCH_DETAILS_total.beta.carotene.xlsx
@@ -478,16 +478,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9826</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3031</v>
+        <v>0.6574</v>
       </c>
       <c r="G2" t="n">
-        <v>84.99939999999999</v>
+        <v>90.19199999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>242.7828</v>
+        <v>251.8925</v>
       </c>
     </row>
     <row r="3">
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.988</v>
+        <v>0.9869</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3149</v>
+        <v>0.6271</v>
       </c>
       <c r="G3" t="n">
-        <v>90.5548</v>
+        <v>92.54810000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>247.4849</v>
+        <v>262.8092</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9802</v>
+        <v>0.9157</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4176</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>101.6348</v>
+        <v>178.2327</v>
       </c>
       <c r="H4" t="n">
-        <v>284.9638</v>
+        <v>286.4363</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.823</v>
+        <v>0.8154</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9272</v>
+        <v>0.1003</v>
       </c>
       <c r="G5" t="n">
-        <v>267.8481</v>
+        <v>272.1768</v>
       </c>
       <c r="H5" t="n">
-        <v>424.6444</v>
+        <v>408.2045</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8292</v>
+        <v>0.7739</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8776</v>
+        <v>0.1566</v>
       </c>
       <c r="G6" t="n">
-        <v>265.2125</v>
+        <v>288.8994</v>
       </c>
       <c r="H6" t="n">
-        <v>413.1256</v>
+        <v>395.2395</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9801</v>
+        <v>0.9553</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3568</v>
+        <v>0.5749</v>
       </c>
       <c r="G7" t="n">
-        <v>98.1326</v>
+        <v>139.2387</v>
       </c>
       <c r="H7" t="n">
-        <v>263.4095</v>
+        <v>280.6037</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9563</v>
+        <v>0.9421</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3957</v>
+        <v>0.5392</v>
       </c>
       <c r="G8" t="n">
-        <v>138.629</v>
+        <v>153.0117</v>
       </c>
       <c r="H8" t="n">
-        <v>277.4093</v>
+        <v>292.1412</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9877</v>
+        <v>0.9849</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3004</v>
+        <v>0.6604</v>
       </c>
       <c r="G9" t="n">
-        <v>84.3352</v>
+        <v>91.36109999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>241.6851</v>
+        <v>250.7792</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9542</v>
+        <v>0.9403</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4002</v>
+        <v>0.5402</v>
       </c>
       <c r="G10" t="n">
-        <v>140.8903</v>
+        <v>155.1143</v>
       </c>
       <c r="H10" t="n">
-        <v>278.971</v>
+        <v>291.8382</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9581</v>
+        <v>0.9401</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3943</v>
+        <v>0.5387</v>
       </c>
       <c r="G11" t="n">
-        <v>136.3509</v>
+        <v>155.2185</v>
       </c>
       <c r="H11" t="n">
-        <v>276.924</v>
+        <v>292.2889</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9707</v>
+        <v>0.9403</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3923</v>
+        <v>0.535</v>
       </c>
       <c r="G12" t="n">
-        <v>117.9594</v>
+        <v>155.2706</v>
       </c>
       <c r="H12" t="n">
-        <v>276.213</v>
+        <v>293.4581</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9574</v>
+        <v>0.9406</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3977</v>
+        <v>0.5347</v>
       </c>
       <c r="G13" t="n">
-        <v>137.3413</v>
+        <v>155.0139</v>
       </c>
       <c r="H13" t="n">
-        <v>278.0967</v>
+        <v>293.5646</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.958</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.395</v>
+        <v>0.5391</v>
       </c>
       <c r="G14" t="n">
-        <v>136.5079</v>
+        <v>155.2986</v>
       </c>
       <c r="H14" t="n">
-        <v>277.1586</v>
+        <v>292.1631</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9708</v>
+        <v>0.9405</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3904</v>
+        <v>0.5352</v>
       </c>
       <c r="G15" t="n">
-        <v>117.9355</v>
+        <v>155.1688</v>
       </c>
       <c r="H15" t="n">
-        <v>275.5403</v>
+        <v>293.4083</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9575</v>
+        <v>0.9408</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3927</v>
+        <v>0.5349</v>
       </c>
       <c r="G16" t="n">
-        <v>136.8027</v>
+        <v>154.8672</v>
       </c>
       <c r="H16" t="n">
-        <v>276.3548</v>
+        <v>293.5155</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9386</v>
       </c>
       <c r="F17" t="n">
-        <v>1.394</v>
+        <v>0.5367</v>
       </c>
       <c r="G17" t="n">
-        <v>137.3898</v>
+        <v>155.2662</v>
       </c>
       <c r="H17" t="n">
-        <v>276.8189</v>
+        <v>292.9378</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9848</v>
+        <v>0.9756</v>
       </c>
       <c r="F18" t="n">
-        <v>1.308</v>
+        <v>0.6421</v>
       </c>
       <c r="G18" t="n">
-        <v>87.6422</v>
+        <v>105.7624</v>
       </c>
       <c r="H18" t="n">
-        <v>244.7522</v>
+        <v>257.4656</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9841</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3053</v>
+        <v>0.6369</v>
       </c>
       <c r="G19" t="n">
-        <v>90.82470000000001</v>
+        <v>93.9496</v>
       </c>
       <c r="H19" t="n">
-        <v>243.6615</v>
+        <v>259.3236</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9839</v>
+        <v>0.958</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3136</v>
+        <v>0.6369</v>
       </c>
       <c r="G20" t="n">
-        <v>90.0939</v>
+        <v>132.2036</v>
       </c>
       <c r="H20" t="n">
-        <v>246.9445</v>
+        <v>259.331</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9837</v>
+        <v>0.9806</v>
       </c>
       <c r="F21" t="n">
-        <v>1.324</v>
+        <v>0.6331</v>
       </c>
       <c r="G21" t="n">
-        <v>90.28919999999999</v>
+        <v>94.4348</v>
       </c>
       <c r="H21" t="n">
-        <v>251.0179</v>
+        <v>260.6955</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9832</v>
+        <v>0.9685</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3253</v>
+        <v>0.6262</v>
       </c>
       <c r="G22" t="n">
-        <v>92.0608</v>
+        <v>115.9817</v>
       </c>
       <c r="H22" t="n">
-        <v>251.5207</v>
+        <v>263.1341</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.982</v>
+        <v>0.9519</v>
       </c>
       <c r="F23" t="n">
-        <v>1.323</v>
+        <v>0.6206</v>
       </c>
       <c r="G23" t="n">
-        <v>95.0802</v>
+        <v>143.5982</v>
       </c>
       <c r="H23" t="n">
-        <v>250.6197</v>
+        <v>265.0951</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9821</v>
+        <v>0.9677</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3299</v>
+        <v>0.6161</v>
       </c>
       <c r="G24" t="n">
-        <v>92.8065</v>
+        <v>118.3106</v>
       </c>
       <c r="H24" t="n">
-        <v>253.2946</v>
+        <v>266.6616</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9805</v>
+        <v>0.9522</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3302</v>
+        <v>0.6237</v>
       </c>
       <c r="G25" t="n">
-        <v>96.82729999999999</v>
+        <v>142.6727</v>
       </c>
       <c r="H25" t="n">
-        <v>253.4179</v>
+        <v>264.0144</v>
       </c>
     </row>
     <row r="26">
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9858</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2929</v>
+        <v>0.6401</v>
       </c>
       <c r="G26" t="n">
-        <v>85.0137</v>
+        <v>89.0675</v>
       </c>
       <c r="H26" t="n">
-        <v>238.6477</v>
+        <v>258.1817</v>
       </c>
     </row>
     <row r="27">
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9852</v>
+        <v>0.9808</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3066</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>88.79859999999999</v>
+        <v>93.0445</v>
       </c>
       <c r="H27" t="n">
-        <v>244.2007</v>
+        <v>257.29</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9849</v>
+        <v>0.98</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3047</v>
+        <v>0.6482</v>
       </c>
       <c r="G28" t="n">
-        <v>87.96420000000001</v>
+        <v>95.6361</v>
       </c>
       <c r="H28" t="n">
-        <v>243.4164</v>
+        <v>255.2684</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9842</v>
+        <v>0.9708</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3093</v>
+        <v>0.6466</v>
       </c>
       <c r="G29" t="n">
-        <v>91.289</v>
+        <v>112.2553</v>
       </c>
       <c r="H29" t="n">
-        <v>245.276</v>
+        <v>255.8497</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9846</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3055</v>
+        <v>0.6365</v>
       </c>
       <c r="G30" t="n">
-        <v>88.2581</v>
+        <v>98.492</v>
       </c>
       <c r="H30" t="n">
-        <v>243.7664</v>
+        <v>259.4734</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9829</v>
+        <v>0.982</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3155</v>
+        <v>0.6248</v>
       </c>
       <c r="G31" t="n">
-        <v>91.1857</v>
+        <v>93.00830000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>247.697</v>
+        <v>263.6297</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9819</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3158</v>
+        <v>0.6189</v>
       </c>
       <c r="G32" t="n">
-        <v>95.2513</v>
+        <v>95.6469</v>
       </c>
       <c r="H32" t="n">
-        <v>247.8144</v>
+        <v>265.6632</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9808</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3172</v>
+        <v>0.6233</v>
       </c>
       <c r="G33" t="n">
-        <v>93.6559</v>
+        <v>95.18129999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>248.3654</v>
+        <v>264.1538</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9816</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3544</v>
+        <v>0.6222</v>
       </c>
       <c r="G34" t="n">
-        <v>108.8336</v>
+        <v>97.5651</v>
       </c>
       <c r="H34" t="n">
-        <v>262.5231</v>
+        <v>264.5227</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9852</v>
+        <v>0.9838</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3343</v>
+        <v>0.6335</v>
       </c>
       <c r="G35" t="n">
-        <v>92.81229999999999</v>
+        <v>97.09739999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>254.9906</v>
+        <v>260.5212</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9869</v>
+        <v>0.9805</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3088</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>94.2372</v>
+        <v>101.338</v>
       </c>
       <c r="H36" t="n">
-        <v>245.0416</v>
+        <v>254.3567</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9866</v>
+        <v>0.9785</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2967</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>86.1853</v>
+        <v>103.4328</v>
       </c>
       <c r="H37" t="n">
-        <v>240.2254</v>
+        <v>254.356</v>
       </c>
     </row>
     <row r="38">
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9868</v>
+        <v>0.9858</v>
       </c>
       <c r="F38" t="n">
-        <v>1.2936</v>
+        <v>0.6583</v>
       </c>
       <c r="G38" t="n">
-        <v>84.74339999999999</v>
+        <v>87.19540000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>238.9685</v>
+        <v>251.5562</v>
       </c>
     </row>
     <row r="39">
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9853</v>
+        <v>0.9841</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3003</v>
+        <v>0.6442</v>
       </c>
       <c r="G39" t="n">
-        <v>88.0639</v>
+        <v>90.25320000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>241.6437</v>
+        <v>256.7222</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9848</v>
+        <v>0.9769</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3205</v>
+        <v>0.6293</v>
       </c>
       <c r="G40" t="n">
-        <v>89.1498</v>
+        <v>107.0202</v>
       </c>
       <c r="H40" t="n">
-        <v>249.671</v>
+        <v>262.0179</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9818</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3553</v>
+        <v>0.6213</v>
       </c>
       <c r="G41" t="n">
-        <v>108.7932</v>
+        <v>97.3948</v>
       </c>
       <c r="H41" t="n">
-        <v>262.8632</v>
+        <v>264.8334</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9852</v>
+        <v>0.9839</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3348</v>
+        <v>0.6296</v>
       </c>
       <c r="G42" t="n">
-        <v>92.9547</v>
+        <v>96.7723</v>
       </c>
       <c r="H42" t="n">
-        <v>255.1618</v>
+        <v>261.9048</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9868</v>
+        <v>0.9807</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3084</v>
+        <v>0.6501</v>
       </c>
       <c r="G43" t="n">
-        <v>93.1755</v>
+        <v>101.7803</v>
       </c>
       <c r="H43" t="n">
-        <v>244.8992</v>
+        <v>254.5835</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9868</v>
+        <v>0.9791</v>
       </c>
       <c r="F44" t="n">
-        <v>1.297</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>85.69580000000001</v>
+        <v>103.0426</v>
       </c>
       <c r="H44" t="n">
-        <v>240.3427</v>
+        <v>254.3636</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9867</v>
+        <v>0.9861</v>
       </c>
       <c r="F45" t="n">
-        <v>1.2928</v>
+        <v>0.6632</v>
       </c>
       <c r="G45" t="n">
-        <v>83.88849999999999</v>
+        <v>86.3082</v>
       </c>
       <c r="H45" t="n">
-        <v>238.6262</v>
+        <v>249.7503</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9851</v>
+        <v>0.9752</v>
       </c>
       <c r="F46" t="n">
-        <v>1.3067</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>89.22750000000001</v>
+        <v>105.846</v>
       </c>
       <c r="H46" t="n">
-        <v>244.2271</v>
+        <v>257.642</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9846</v>
+        <v>0.9777</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3228</v>
+        <v>0.6274</v>
       </c>
       <c r="G47" t="n">
-        <v>89.7504</v>
+        <v>105.8311</v>
       </c>
       <c r="H47" t="n">
-        <v>250.5579</v>
+        <v>262.702</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9855</v>
+        <v>0.9832</v>
       </c>
       <c r="F48" t="n">
-        <v>1.316</v>
+        <v>0.6411</v>
       </c>
       <c r="G48" t="n">
-        <v>91.2944</v>
+        <v>93.65900000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>247.889</v>
+        <v>257.8146</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9765</v>
       </c>
       <c r="F49" t="n">
-        <v>1.3083</v>
+        <v>0.661</v>
       </c>
       <c r="G49" t="n">
-        <v>87.354</v>
+        <v>108.6908</v>
       </c>
       <c r="H49" t="n">
-        <v>244.8483</v>
+        <v>250.5648</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9261</v>
       </c>
       <c r="F50" t="n">
-        <v>1.7551</v>
+        <v>0.1838</v>
       </c>
       <c r="G50" t="n">
-        <v>201.5565</v>
+        <v>206.6523</v>
       </c>
       <c r="H50" t="n">
-        <v>383.2076</v>
+        <v>388.8044</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.9684</v>
+        <v>0.8831</v>
       </c>
       <c r="F51" t="n">
-        <v>1.8188</v>
+        <v>0.0987</v>
       </c>
       <c r="G51" t="n">
-        <v>147.8475</v>
+        <v>240.91</v>
       </c>
       <c r="H51" t="n">
-        <v>399.0554</v>
+        <v>408.5781</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9669</v>
+        <v>0.82</v>
       </c>
       <c r="F52" t="n">
-        <v>1.8127</v>
+        <v>0.1061</v>
       </c>
       <c r="G52" t="n">
-        <v>150.2996</v>
+        <v>280.0712</v>
       </c>
       <c r="H52" t="n">
-        <v>397.5567</v>
+        <v>406.892</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.947</v>
+        <v>0.914</v>
       </c>
       <c r="F53" t="n">
-        <v>1.7933</v>
+        <v>0.1458</v>
       </c>
       <c r="G53" t="n">
-        <v>185.1054</v>
+        <v>215.5316</v>
       </c>
       <c r="H53" t="n">
-        <v>392.7782</v>
+        <v>397.7623</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8994</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>1.7714</v>
+        <v>0.1862</v>
       </c>
       <c r="G54" t="n">
-        <v>232.1317</v>
+        <v>219.3276</v>
       </c>
       <c r="H54" t="n">
-        <v>387.3201</v>
+        <v>388.2426</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9717</v>
+        <v>0.8763</v>
       </c>
       <c r="F55" t="n">
-        <v>1.8518</v>
+        <v>0.0473</v>
       </c>
       <c r="G55" t="n">
-        <v>154.2184</v>
+        <v>271.1609</v>
       </c>
       <c r="H55" t="n">
-        <v>407.0072</v>
+        <v>420.061</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>1.8621</v>
+        <v>0.049</v>
       </c>
       <c r="G56" t="n">
-        <v>185.5029</v>
+        <v>261.3821</v>
       </c>
       <c r="H56" t="n">
-        <v>409.4665</v>
+        <v>419.6836</v>
       </c>
     </row>
     <row r="57">
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.8939</v>
+        <v>0.8943</v>
       </c>
       <c r="F57" t="n">
-        <v>1.8454</v>
+        <v>0.1078</v>
       </c>
       <c r="G57" t="n">
-        <v>239.302</v>
+        <v>238.7253</v>
       </c>
       <c r="H57" t="n">
-        <v>405.465</v>
+        <v>406.516</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8267</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>1.8786</v>
+        <v>0.1548</v>
       </c>
       <c r="G58" t="n">
-        <v>266.5484</v>
+        <v>288.7258</v>
       </c>
       <c r="H58" t="n">
-        <v>413.3565</v>
+        <v>395.6619</v>
       </c>
     </row>
     <row r="59">
@@ -2302,16 +2302,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.792</v>
+        <v>0.7732</v>
       </c>
       <c r="F59" t="n">
-        <v>1.881</v>
+        <v>0.1526</v>
       </c>
       <c r="G59" t="n">
-        <v>285.9397</v>
+        <v>288.986</v>
       </c>
       <c r="H59" t="n">
-        <v>413.9315</v>
+        <v>396.1649</v>
       </c>
     </row>
     <row r="60">
@@ -2334,16 +2334,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.792</v>
+        <v>0.7749</v>
       </c>
       <c r="F60" t="n">
-        <v>1.8811</v>
+        <v>0.1538</v>
       </c>
       <c r="G60" t="n">
-        <v>285.8089</v>
+        <v>288.6248</v>
       </c>
       <c r="H60" t="n">
-        <v>413.9584</v>
+        <v>395.8978</v>
       </c>
     </row>
     <row r="61">
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.7901</v>
+        <v>0.7736</v>
       </c>
       <c r="F61" t="n">
-        <v>1.8855</v>
+        <v>0.1561</v>
       </c>
       <c r="G61" t="n">
-        <v>286.4174</v>
+        <v>288.7096</v>
       </c>
       <c r="H61" t="n">
-        <v>414.9748</v>
+        <v>395.3512</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.873</v>
+        <v>0.8575</v>
       </c>
       <c r="F62" t="n">
-        <v>1.8218</v>
+        <v>0.1517</v>
       </c>
       <c r="G62" t="n">
-        <v>246.317</v>
+        <v>251.9402</v>
       </c>
       <c r="H62" t="n">
-        <v>399.7841</v>
+        <v>396.3729</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8196</v>
       </c>
       <c r="F63" t="n">
-        <v>1.8179</v>
+        <v>0.1541</v>
       </c>
       <c r="G63" t="n">
-        <v>247.2063</v>
+        <v>277.5553</v>
       </c>
       <c r="H63" t="n">
-        <v>398.8272</v>
+        <v>395.8169</v>
       </c>
     </row>
     <row r="64">
@@ -2462,16 +2462,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8321</v>
+        <v>0.8173</v>
       </c>
       <c r="F64" t="n">
-        <v>1.822</v>
+        <v>0.1654</v>
       </c>
       <c r="G64" t="n">
-        <v>270.9963</v>
+        <v>276.9074</v>
       </c>
       <c r="H64" t="n">
-        <v>399.8288</v>
+        <v>393.157</v>
       </c>
     </row>
     <row r="65">
@@ -2494,16 +2494,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8254</v>
+        <v>0.8112</v>
       </c>
       <c r="F65" t="n">
-        <v>1.8224</v>
+        <v>0.1697</v>
       </c>
       <c r="G65" t="n">
-        <v>272.3274</v>
+        <v>277.3508</v>
       </c>
       <c r="H65" t="n">
-        <v>399.9104</v>
+        <v>392.1515</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9157</v>
+        <v>0.8831</v>
       </c>
       <c r="F66" t="n">
-        <v>1.8232</v>
+        <v>0.1021</v>
       </c>
       <c r="G66" t="n">
-        <v>217.0733</v>
+        <v>258.1203</v>
       </c>
       <c r="H66" t="n">
-        <v>400.1251</v>
+        <v>407.7921</v>
       </c>
     </row>
     <row r="67">
@@ -2558,16 +2558,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8924</v>
+        <v>0.8865</v>
       </c>
       <c r="F67" t="n">
-        <v>1.8422</v>
+        <v>0.1136</v>
       </c>
       <c r="G67" t="n">
-        <v>253.4685</v>
+        <v>256.2983</v>
       </c>
       <c r="H67" t="n">
-        <v>404.7145</v>
+        <v>405.1873</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8855</v>
+        <v>0.8991</v>
       </c>
       <c r="F68" t="n">
-        <v>1.8415</v>
+        <v>0.1119</v>
       </c>
       <c r="G68" t="n">
-        <v>250.0693</v>
+        <v>239.5932</v>
       </c>
       <c r="H68" t="n">
-        <v>404.5423</v>
+        <v>405.5729</v>
       </c>
     </row>
     <row r="69">
@@ -2622,16 +2622,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9837</v>
+        <v>0.9813</v>
       </c>
       <c r="F69" t="n">
-        <v>1.3521</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>90.55840000000001</v>
+        <v>94.4311</v>
       </c>
       <c r="H69" t="n">
-        <v>261.6721</v>
+        <v>264.7865</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9838</v>
+        <v>0.9732</v>
       </c>
       <c r="F70" t="n">
-        <v>1.3424</v>
+        <v>0.622</v>
       </c>
       <c r="G70" t="n">
-        <v>90.31359999999999</v>
+        <v>110.2579</v>
       </c>
       <c r="H70" t="n">
-        <v>258.0411</v>
+        <v>264.5833</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9837</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>1.348</v>
+        <v>0.6322</v>
       </c>
       <c r="G71" t="n">
-        <v>90.5667</v>
+        <v>122.0004</v>
       </c>
       <c r="H71" t="n">
-        <v>260.1325</v>
+        <v>260.9906</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9808</v>
+        <v>0.9751</v>
       </c>
       <c r="F72" t="n">
-        <v>1.3342</v>
+        <v>0.6217</v>
       </c>
       <c r="G72" t="n">
-        <v>96.1378</v>
+        <v>107.1016</v>
       </c>
       <c r="H72" t="n">
-        <v>254.9372</v>
+        <v>264.692</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9843</v>
+        <v>0.9828</v>
       </c>
       <c r="F73" t="n">
-        <v>1.3629</v>
+        <v>0.5982</v>
       </c>
       <c r="G73" t="n">
-        <v>96.4875</v>
+        <v>97.99979999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>265.6672</v>
+        <v>272.7944</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9852</v>
+        <v>0.9848</v>
       </c>
       <c r="F74" t="n">
-        <v>1.3479</v>
+        <v>0.6165</v>
       </c>
       <c r="G74" t="n">
-        <v>91.5039</v>
+        <v>91.0652</v>
       </c>
       <c r="H74" t="n">
-        <v>260.1136</v>
+        <v>266.5181</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9729</v>
+        <v>0.9637</v>
       </c>
       <c r="F75" t="n">
-        <v>1.3716</v>
+        <v>0.58</v>
       </c>
       <c r="G75" t="n">
-        <v>113.2153</v>
+        <v>120.717</v>
       </c>
       <c r="H75" t="n">
-        <v>268.8362</v>
+        <v>278.9024</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9729</v>
+        <v>0.9637</v>
       </c>
       <c r="F76" t="n">
-        <v>1.3716</v>
+        <v>0.58</v>
       </c>
       <c r="G76" t="n">
-        <v>113.2153</v>
+        <v>120.717</v>
       </c>
       <c r="H76" t="n">
-        <v>268.8362</v>
+        <v>278.9024</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8756</v>
+        <v>0.8258</v>
       </c>
       <c r="F77" t="n">
-        <v>1.8164</v>
+        <v>0.1494</v>
       </c>
       <c r="G77" t="n">
-        <v>238.2525</v>
+        <v>262.7325</v>
       </c>
       <c r="H77" t="n">
-        <v>398.4714</v>
+        <v>396.9092</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8645</v>
+        <v>0.8219</v>
       </c>
       <c r="F78" t="n">
-        <v>1.8153</v>
+        <v>0.152</v>
       </c>
       <c r="G78" t="n">
-        <v>246.0755</v>
+        <v>265.5224</v>
       </c>
       <c r="H78" t="n">
-        <v>398.1966</v>
+        <v>396.307</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8435</v>
+        <v>0.8227</v>
       </c>
       <c r="F79" t="n">
-        <v>1.8134</v>
+        <v>0.1456</v>
       </c>
       <c r="G79" t="n">
-        <v>258.1432</v>
+        <v>264.9114</v>
       </c>
       <c r="H79" t="n">
-        <v>397.7348</v>
+        <v>397.7909</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8646</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>1.8146</v>
+        <v>0.1515</v>
       </c>
       <c r="G80" t="n">
-        <v>245.9642</v>
+        <v>265.4259</v>
       </c>
       <c r="H80" t="n">
-        <v>398.0147</v>
+        <v>396.4204</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8346</v>
       </c>
       <c r="F81" t="n">
-        <v>1.828</v>
+        <v>0.1036</v>
       </c>
       <c r="G81" t="n">
-        <v>245.7316</v>
+        <v>277.6929</v>
       </c>
       <c r="H81" t="n">
-        <v>401.2864</v>
+        <v>407.4606</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9187</v>
+        <v>0.8472</v>
       </c>
       <c r="F82" t="n">
-        <v>1.8059</v>
+        <v>0.1093</v>
       </c>
       <c r="G82" t="n">
-        <v>213.6923</v>
+        <v>268.996</v>
       </c>
       <c r="H82" t="n">
-        <v>395.9014</v>
+        <v>406.161</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9718</v>
+        <v>0.9479</v>
       </c>
       <c r="F83" t="n">
-        <v>1.3712</v>
+        <v>0.5676</v>
       </c>
       <c r="G83" t="n">
-        <v>115.321</v>
+        <v>142.5328</v>
       </c>
       <c r="H83" t="n">
-        <v>268.6656</v>
+        <v>282.9976</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9716</v>
+        <v>0.9473</v>
       </c>
       <c r="F84" t="n">
-        <v>1.3753</v>
+        <v>0.5652</v>
       </c>
       <c r="G84" t="n">
-        <v>115.658</v>
+        <v>143.3104</v>
       </c>
       <c r="H84" t="n">
-        <v>270.1676</v>
+        <v>283.7804</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.972</v>
+        <v>0.9474</v>
       </c>
       <c r="F85" t="n">
-        <v>1.3704</v>
+        <v>0.5679</v>
       </c>
       <c r="G85" t="n">
-        <v>115.0063</v>
+        <v>143.2957</v>
       </c>
       <c r="H85" t="n">
-        <v>268.3743</v>
+        <v>282.895</v>
       </c>
     </row>
     <row r="86">
@@ -3166,16 +3166,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9697</v>
       </c>
       <c r="F86" t="n">
-        <v>1.3242</v>
+        <v>0.6403</v>
       </c>
       <c r="G86" t="n">
-        <v>109.343</v>
+        <v>113.4005</v>
       </c>
       <c r="H86" t="n">
-        <v>251.1031</v>
+        <v>258.1047</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9852</v>
+        <v>0.9724</v>
       </c>
       <c r="F87" t="n">
-        <v>1.324</v>
+        <v>0.6323</v>
       </c>
       <c r="G87" t="n">
-        <v>88.0476</v>
+        <v>112.7175</v>
       </c>
       <c r="H87" t="n">
-        <v>251.0207</v>
+        <v>260.9542</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9845</v>
+        <v>0.98</v>
       </c>
       <c r="F88" t="n">
-        <v>1.3118</v>
+        <v>0.6422</v>
       </c>
       <c r="G88" t="n">
-        <v>89.09399999999999</v>
+        <v>95.7612</v>
       </c>
       <c r="H88" t="n">
-        <v>246.26</v>
+        <v>257.4264</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9849</v>
+        <v>0.9525</v>
       </c>
       <c r="F89" t="n">
-        <v>1.3215</v>
+        <v>0.6292</v>
       </c>
       <c r="G89" t="n">
-        <v>87.98609999999999</v>
+        <v>143.9922</v>
       </c>
       <c r="H89" t="n">
-        <v>250.062</v>
+        <v>262.0598</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9868</v>
+        <v>0.9807</v>
       </c>
       <c r="F90" t="n">
-        <v>1.3082</v>
+        <v>0.65</v>
       </c>
       <c r="G90" t="n">
-        <v>93.1755</v>
+        <v>101.7803</v>
       </c>
       <c r="H90" t="n">
-        <v>244.8195</v>
+        <v>254.5916</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9868</v>
+        <v>0.9791</v>
       </c>
       <c r="F91" t="n">
-        <v>1.2969</v>
+        <v>0.6508</v>
       </c>
       <c r="G91" t="n">
-        <v>85.7488</v>
+        <v>103.0426</v>
       </c>
       <c r="H91" t="n">
-        <v>240.2948</v>
+        <v>254.3056</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9845</v>
+        <v>0.98</v>
       </c>
       <c r="F92" t="n">
-        <v>1.3118</v>
+        <v>0.6422</v>
       </c>
       <c r="G92" t="n">
-        <v>89.09399999999999</v>
+        <v>95.7612</v>
       </c>
       <c r="H92" t="n">
-        <v>246.26</v>
+        <v>257.4264</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9868</v>
+        <v>0.9791</v>
       </c>
       <c r="F93" t="n">
-        <v>1.2969</v>
+        <v>0.6508</v>
       </c>
       <c r="G93" t="n">
-        <v>85.7488</v>
+        <v>103.0426</v>
       </c>
       <c r="H93" t="n">
-        <v>240.2948</v>
+        <v>254.3056</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9802</v>
+        <v>0.9157</v>
       </c>
       <c r="F94" t="n">
-        <v>1.4176</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>101.6348</v>
+        <v>178.2327</v>
       </c>
       <c r="H94" t="n">
-        <v>284.9638</v>
+        <v>286.4363</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.9287</v>
+        <v>0.8216</v>
       </c>
       <c r="F95" t="n">
-        <v>2.0817</v>
+        <v>-0.1373</v>
       </c>
       <c r="G95" t="n">
-        <v>227.5826</v>
+        <v>285.849</v>
       </c>
       <c r="H95" t="n">
-        <v>458.6506</v>
+        <v>458.958</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9173</v>
       </c>
       <c r="F96" t="n">
-        <v>1.4196</v>
+        <v>0.5623</v>
       </c>
       <c r="G96" t="n">
-        <v>104.3345</v>
+        <v>176.9659</v>
       </c>
       <c r="H96" t="n">
-        <v>285.6727</v>
+        <v>284.7298</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9776</v>
+        <v>0.9166</v>
       </c>
       <c r="F97" t="n">
-        <v>1.4181</v>
+        <v>0.5646</v>
       </c>
       <c r="G97" t="n">
-        <v>103.6314</v>
+        <v>177.5163</v>
       </c>
       <c r="H97" t="n">
-        <v>285.1525</v>
+        <v>283.9704</v>
       </c>
     </row>
     <row r="98">
@@ -3550,16 +3550,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9748</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>1.3067</v>
+        <v>0.649</v>
       </c>
       <c r="G98" t="n">
-        <v>109.6479</v>
+        <v>110.1218</v>
       </c>
       <c r="H98" t="n">
-        <v>244.2208</v>
+        <v>254.9759</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9762</v>
+        <v>0.9759</v>
       </c>
       <c r="F99" t="n">
-        <v>1.2915</v>
+        <v>0.649</v>
       </c>
       <c r="G99" t="n">
-        <v>106.4958</v>
+        <v>104.5404</v>
       </c>
       <c r="H99" t="n">
-        <v>238.077</v>
+        <v>254.9744</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9784</v>
+        <v>0.9762</v>
       </c>
       <c r="F100" t="n">
-        <v>1.3105</v>
+        <v>0.6342</v>
       </c>
       <c r="G100" t="n">
-        <v>103.2454</v>
+        <v>105.1347</v>
       </c>
       <c r="H100" t="n">
-        <v>245.738</v>
+        <v>260.3053</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9756</v>
+        <v>0.9574</v>
       </c>
       <c r="F101" t="n">
-        <v>1.3139</v>
+        <v>0.6229</v>
       </c>
       <c r="G101" t="n">
-        <v>109.0375</v>
+        <v>131.8257</v>
       </c>
       <c r="H101" t="n">
-        <v>247.0704</v>
+        <v>264.2794</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9819</v>
+        <v>0.9796</v>
       </c>
       <c r="F102" t="n">
-        <v>1.3276</v>
+        <v>0.6186</v>
       </c>
       <c r="G102" t="n">
-        <v>97.9212</v>
+        <v>97.41330000000001</v>
       </c>
       <c r="H102" t="n">
-        <v>252.3907</v>
+        <v>265.7695</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9795</v>
+        <v>0.978</v>
       </c>
       <c r="F103" t="n">
-        <v>1.3055</v>
+        <v>0.6435</v>
       </c>
       <c r="G103" t="n">
-        <v>104.1047</v>
+        <v>98.45050000000001</v>
       </c>
       <c r="H103" t="n">
-        <v>243.754</v>
+        <v>256.9576</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9847</v>
+        <v>0.9798</v>
       </c>
       <c r="F104" t="n">
-        <v>1.2986</v>
+        <v>0.6577</v>
       </c>
       <c r="G104" t="n">
-        <v>91.8711</v>
+        <v>95.0538</v>
       </c>
       <c r="H104" t="n">
-        <v>240.9913</v>
+        <v>251.7822</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9796</v>
+        <v>0.9648</v>
       </c>
       <c r="F105" t="n">
-        <v>1.2948</v>
+        <v>0.6483</v>
       </c>
       <c r="G105" t="n">
-        <v>101.2133</v>
+        <v>124.9037</v>
       </c>
       <c r="H105" t="n">
-        <v>239.4496</v>
+        <v>255.2189</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9819</v>
+        <v>0.977</v>
       </c>
       <c r="F106" t="n">
-        <v>1.2898</v>
+        <v>0.6448</v>
       </c>
       <c r="G106" t="n">
-        <v>93.8601</v>
+        <v>103.3246</v>
       </c>
       <c r="H106" t="n">
-        <v>237.3817</v>
+        <v>256.4877</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9685</v>
       </c>
       <c r="F107" t="n">
-        <v>1.3067</v>
+        <v>0.6407</v>
       </c>
       <c r="G107" t="n">
-        <v>106.9456</v>
+        <v>119.1932</v>
       </c>
       <c r="H107" t="n">
-        <v>244.2215</v>
+        <v>257.971</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9734</v>
       </c>
       <c r="F108" t="n">
-        <v>1.3623</v>
+        <v>0.5914</v>
       </c>
       <c r="G108" t="n">
-        <v>96.0966</v>
+        <v>120.2671</v>
       </c>
       <c r="H108" t="n">
-        <v>265.4489</v>
+        <v>275.0957</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9859</v>
+        <v>0.9739</v>
       </c>
       <c r="F109" t="n">
-        <v>1.3378</v>
+        <v>0.6194</v>
       </c>
       <c r="G109" t="n">
-        <v>93.877</v>
+        <v>116.8827</v>
       </c>
       <c r="H109" t="n">
-        <v>256.3082</v>
+        <v>265.4868</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9855</v>
+        <v>0.979</v>
       </c>
       <c r="F110" t="n">
-        <v>1.3141</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>90.9375</v>
+        <v>105.3389</v>
       </c>
       <c r="H110" t="n">
-        <v>247.1612</v>
+        <v>254.6997</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9856</v>
+        <v>0.9835</v>
       </c>
       <c r="F111" t="n">
-        <v>1.3205</v>
+        <v>0.6229</v>
       </c>
       <c r="G111" t="n">
-        <v>90.53879999999999</v>
+        <v>91.4757</v>
       </c>
       <c r="H111" t="n">
-        <v>249.6726</v>
+        <v>264.2636</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>1.362</v>
+        <v>0.5906</v>
       </c>
       <c r="G112" t="n">
-        <v>96.0967</v>
+        <v>120.3247</v>
       </c>
       <c r="H112" t="n">
-        <v>265.3187</v>
+        <v>275.353</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9859</v>
+        <v>0.9794</v>
       </c>
       <c r="F113" t="n">
-        <v>1.3378</v>
+        <v>0.6162</v>
       </c>
       <c r="G113" t="n">
-        <v>93.7349</v>
+        <v>107.5743</v>
       </c>
       <c r="H113" t="n">
-        <v>256.3257</v>
+        <v>266.6253</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9825</v>
       </c>
       <c r="F114" t="n">
-        <v>1.3196</v>
+        <v>0.6538</v>
       </c>
       <c r="G114" t="n">
-        <v>90.8571</v>
+        <v>93.6915</v>
       </c>
       <c r="H114" t="n">
-        <v>249.3044</v>
+        <v>253.234</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9835</v>
       </c>
       <c r="F115" t="n">
-        <v>1.3215</v>
+        <v>0.6271</v>
       </c>
       <c r="G115" t="n">
-        <v>90.7064</v>
+        <v>90.91079999999999</v>
       </c>
       <c r="H115" t="n">
-        <v>250.0428</v>
+        <v>262.815</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.8243</v>
       </c>
       <c r="F116" t="n">
-        <v>1.8713</v>
+        <v>0.0413</v>
       </c>
       <c r="G116" t="n">
-        <v>151.8694</v>
+        <v>288.0324</v>
       </c>
       <c r="H116" t="n">
-        <v>411.6475</v>
+        <v>421.3777</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.967</v>
+        <v>0.8153</v>
       </c>
       <c r="F117" t="n">
-        <v>1.8654</v>
+        <v>0.0245</v>
       </c>
       <c r="G117" t="n">
-        <v>157.9737</v>
+        <v>291.4929</v>
       </c>
       <c r="H117" t="n">
-        <v>410.2496</v>
+        <v>425.0565</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9796</v>
+        <v>0.9648</v>
       </c>
       <c r="F118" t="n">
-        <v>1.2948</v>
+        <v>0.6483</v>
       </c>
       <c r="G118" t="n">
-        <v>101.2133</v>
+        <v>124.9037</v>
       </c>
       <c r="H118" t="n">
-        <v>239.4496</v>
+        <v>255.2189</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9859</v>
+        <v>0.9794</v>
       </c>
       <c r="F119" t="n">
-        <v>1.3378</v>
+        <v>0.6162</v>
       </c>
       <c r="G119" t="n">
-        <v>93.7349</v>
+        <v>107.5743</v>
       </c>
       <c r="H119" t="n">
-        <v>256.3257</v>
+        <v>266.6253</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9603</v>
+        <v>0.9165</v>
       </c>
       <c r="F120" t="n">
-        <v>1.3844</v>
+        <v>0.5643</v>
       </c>
       <c r="G120" t="n">
-        <v>133.5987</v>
+        <v>178.9346</v>
       </c>
       <c r="H120" t="n">
-        <v>273.4298</v>
+        <v>284.0843</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9603</v>
+        <v>0.9165</v>
       </c>
       <c r="F121" t="n">
-        <v>1.3844</v>
+        <v>0.5643</v>
       </c>
       <c r="G121" t="n">
-        <v>133.5987</v>
+        <v>178.9346</v>
       </c>
       <c r="H121" t="n">
-        <v>273.4298</v>
+        <v>284.0843</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9816</v>
+        <v>0.9815</v>
       </c>
       <c r="F122" t="n">
-        <v>1.3181</v>
+        <v>0.6423</v>
       </c>
       <c r="G122" t="n">
-        <v>95.33329999999999</v>
+        <v>95.0326</v>
       </c>
       <c r="H122" t="n">
-        <v>248.741</v>
+        <v>257.3999</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9859</v>
+        <v>0.9794</v>
       </c>
       <c r="F123" t="n">
-        <v>1.3379</v>
+        <v>0.616</v>
       </c>
       <c r="G123" t="n">
-        <v>93.7483</v>
+        <v>107.6676</v>
       </c>
       <c r="H123" t="n">
-        <v>256.339</v>
+        <v>266.6891</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9857</v>
+        <v>0.9847</v>
       </c>
       <c r="F124" t="n">
-        <v>1.3226</v>
+        <v>0.6643</v>
       </c>
       <c r="G124" t="n">
-        <v>91.43129999999999</v>
+        <v>88.79859999999999</v>
       </c>
       <c r="H124" t="n">
-        <v>250.4622</v>
+        <v>249.3668</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.976</v>
       </c>
       <c r="F125" t="n">
-        <v>1.3185</v>
+        <v>0.6375</v>
       </c>
       <c r="G125" t="n">
-        <v>89.59480000000001</v>
+        <v>102.3846</v>
       </c>
       <c r="H125" t="n">
-        <v>248.8902</v>
+        <v>259.0992</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9836</v>
+        <v>0.9609</v>
       </c>
       <c r="F126" t="n">
-        <v>1.3758</v>
+        <v>0.5859</v>
       </c>
       <c r="G126" t="n">
-        <v>97.7538</v>
+        <v>138.2058</v>
       </c>
       <c r="H126" t="n">
-        <v>270.3472</v>
+        <v>276.9504</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9851</v>
+        <v>0.9807</v>
       </c>
       <c r="F127" t="n">
-        <v>1.3006</v>
+        <v>0.6512</v>
       </c>
       <c r="G127" t="n">
-        <v>92.2045</v>
+        <v>101.9188</v>
       </c>
       <c r="H127" t="n">
-        <v>241.7878</v>
+        <v>254.159</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.beta.carotene/RANDOMSEARCH_DETAILS_total.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.beta.carotene/RANDOMSEARCH_DETAILS_total.beta.carotene.xlsx
@@ -570,17 +570,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8154</v>
+        <v>0.8153</v>
       </c>
       <c r="F5" t="n">
         <v>0.1003</v>
       </c>
       <c r="G5" t="n">
-        <v>272.1768</v>
+        <v>272.1982</v>
       </c>
       <c r="H5" t="n">
         <v>408.2045</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E96" t="n">
